--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26967,7 +26967,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31461,7 +31461,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
